--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Mistral-Small-3.2-24B-Instruct-2506/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Mistral-Small-3.2-24B-Instruct-2506/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="E2">
         <v>8</v>
       </c>
       <c r="G2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D3">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H3">
         <v>426</v>
